--- a/experiment/HAT_bestx4/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/HAT_bestx4/Test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.58</v>
+        <v>27.62</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7664</v>
+        <v>0.7677</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.72</v>
+        <v>26.81</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8179</v>
+        <v>0.8208</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.89</v>
+        <v>23.91</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6893</v>
+        <v>0.6914</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.19</v>
+        <v>23.12</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8328</v>
+        <v>0.8323</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.04</v>
+        <v>28.18</v>
       </c>
       <c r="C6" t="n">
-        <v>0.951</v>
+        <v>0.9526</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.44</v>
+        <v>22.5</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6269</v>
+        <v>0.6289</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.58</v>
+        <v>29.62</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8616</v>
+        <v>0.8627</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.53</v>
+        <v>21.59</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6641</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33.85</v>
+        <v>33.81</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9246</v>
+        <v>0.9232</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.29</v>
+        <v>27.38</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8877</v>
+        <v>0.8895</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.82</v>
+        <v>17.48</v>
       </c>
       <c r="C12" t="n">
-        <v>0.798</v>
+        <v>0.7879</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.9</v>
+        <v>23.92</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7348</v>
+        <v>0.7378</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.59</v>
+        <v>29.63</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8393</v>
+        <v>0.8406</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.35</v>
+        <v>22.36</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6876</v>
+        <v>0.6893</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26.26</v>
+        <v>26.34</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7396</v>
+        <v>0.7413999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.29</v>
+        <v>30.46</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9143</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.71</v>
+        <v>25.78</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8276</v>
+        <v>0.8297</v>
       </c>
     </row>
     <row r="19">
@@ -676,7 +676,7 @@
         <v>26.4</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7143</v>
+        <v>0.7149</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.14</v>
+        <v>22.23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8176</v>
+        <v>0.8204</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.15</v>
+        <v>22.17</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7184</v>
+        <v>0.7196</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29.64</v>
+        <v>29.67</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7845</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26.08</v>
+        <v>26.1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7601</v>
+        <v>0.7609</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.47</v>
+        <v>30.42</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9166</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.95</v>
+        <v>20.02</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6503</v>
+        <v>0.6526</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.07</v>
+        <v>32.24</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9016</v>
+        <v>0.9032</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.9</v>
+        <v>27.98</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7047</v>
+        <v>0.7062</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.36</v>
+        <v>28.42</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7978</v>
+        <v>0.7996</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.41</v>
+        <v>31.43</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8767</v>
+        <v>0.8771</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27.32</v>
+        <v>27.38</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8723</v>
+        <v>0.8746</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24.59</v>
+        <v>24.65</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8088</v>
+        <v>0.8117</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24.3</v>
+        <v>24.33</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7926</v>
+        <v>0.7939000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.23</v>
+        <v>29.33</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8602</v>
+        <v>0.8627</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.35</v>
+        <v>27.42</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8088</v>
+        <v>0.8109</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23.09</v>
+        <v>23.1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.587</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.22</v>
+        <v>29.21</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8797</v>
+        <v>0.8811</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         <v>28.86</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8862</v>
+        <v>0.8868</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.52</v>
+        <v>26.53</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8025</v>
+        <v>0.8031</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27</v>
+        <v>27.04</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6814</v>
+        <v>0.6824</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>23</v>
+        <v>23.04</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7407</v>
+        <v>0.7433</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27.01</v>
+        <v>27.05</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9402</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.47</v>
+        <v>26.51</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.8873</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.68</v>
+        <v>28.6</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8851</v>
+        <v>0.8847</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32.08</v>
+        <v>32.42</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9354</v>
+        <v>0.9368</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.61</v>
+        <v>31.78</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8659</v>
+        <v>0.8688</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.12</v>
+        <v>23.93</v>
       </c>
       <c r="C46" t="n">
-        <v>0.714</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.68</v>
+        <v>23.71</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.7624</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21.98</v>
+        <v>22.01</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7744</v>
+        <v>0.7771</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.29</v>
+        <v>20.32</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8163</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.61</v>
+        <v>23.65</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7562</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25.36</v>
+        <v>25.38</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7755</v>
+        <v>0.7763</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27.44</v>
+        <v>27.46</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8489</v>
+        <v>0.8495</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28.86</v>
+        <v>28.88</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9082</v>
+        <v>0.9095</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22.4</v>
+        <v>22.44</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7294</v>
+        <v>0.7311</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>21.19</v>
+        <v>21.23</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6504</v>
+        <v>0.6526999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>33.32</v>
+        <v>33.47</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9479</v>
+        <v>0.9493</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.01</v>
+        <v>25.05</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>30.97</v>
+        <v>31.08</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8952</v>
+        <v>0.8971</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25.87</v>
+        <v>25.92</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8589</v>
+        <v>0.8604000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>22.05</v>
+        <v>22.12</v>
       </c>
       <c r="C60" t="n">
-        <v>0.763</v>
+        <v>0.7658</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22.57</v>
+        <v>22.59</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5692</v>
+        <v>0.5714</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24.83</v>
+        <v>24.79</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7617</v>
+        <v>0.7616000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>21.91</v>
+        <v>21.97</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8128</v>
+        <v>0.8159</v>
       </c>
     </row>
     <row r="64">
@@ -1261,7 +1261,7 @@
         <v>22.48</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6212</v>
+        <v>0.6206</v>
       </c>
     </row>
     <row r="65">
@@ -1274,7 +1274,7 @@
         <v>26.52</v>
       </c>
       <c r="C65" t="n">
-        <v>0.782</v>
+        <v>0.7819</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1287,7 @@
         <v>25.44</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7234</v>
+        <v>0.7239</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>22.17</v>
+        <v>22.15</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6404</v>
+        <v>0.6395999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>19.45</v>
+        <v>19.34</v>
       </c>
       <c r="C68" t="n">
-        <v>0.876</v>
+        <v>0.8751</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30.22</v>
+        <v>30.3</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8853</v>
+        <v>0.8875</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>24.77</v>
+        <v>24.78</v>
       </c>
       <c r="C70" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>22.13</v>
+        <v>22.15</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5965</v>
+        <v>0.5974</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>28.07</v>
+        <v>28.15</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6705</v>
+        <v>0.6734</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>20.11</v>
+        <v>20.18</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8195</v>
+        <v>0.8225</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>20.14</v>
+        <v>20.16</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5715</v>
+        <v>0.5735</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23.84</v>
+        <v>23.87</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7181</v>
+        <v>0.7229</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8858</v>
+        <v>0.8868</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>23.03</v>
+        <v>23.12</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7375</v>
+        <v>0.7433999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.72</v>
+        <v>22.73</v>
       </c>
       <c r="C78" t="n">
-        <v>0.675</v>
+        <v>0.6761</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>27.28</v>
+        <v>27.32</v>
       </c>
       <c r="C79" t="n">
-        <v>0.772</v>
+        <v>0.7734</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>25.45</v>
+        <v>25.47</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6974</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.69</v>
+        <v>35.72</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9534</v>
+        <v>0.9535</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>37.67</v>
+        <v>37.96</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9737</v>
+        <v>0.9747</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>32.92</v>
+        <v>32.97</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9416</v>
+        <v>0.9423</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.34</v>
+        <v>22.37</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7047</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>28.67</v>
+        <v>28.71</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8107</v>
+        <v>0.8118</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>28.33</v>
+        <v>28.41</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9032</v>
+        <v>0.9041</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30.26</v>
+        <v>30.29</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8834</v>
+        <v>0.8829</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.59</v>
+        <v>27.69</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8828</v>
+        <v>0.8842</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>19.88</v>
+        <v>19.9</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5709</v>
+        <v>0.5718</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26.77</v>
+        <v>26.8</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7185</v>
+        <v>0.7204</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37.83</v>
+        <v>37.91</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9756</v>
+        <v>0.976</v>
       </c>
     </row>
     <row r="92">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>23.94</v>
+        <v>23.93</v>
       </c>
       <c r="C92" t="n">
         <v>0.6781</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>18.76</v>
+        <v>18.77</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6492</v>
+        <v>0.6512</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>28.86</v>
+        <v>29.29</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9261</v>
+        <v>0.9296</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>27.15</v>
+        <v>27.18</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7837</v>
+        <v>0.7844</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20.12</v>
+        <v>20.13</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4463</v>
+        <v>0.4458</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>25.28</v>
+        <v>25.42</v>
       </c>
       <c r="C97" t="n">
-        <v>0.869</v>
+        <v>0.8716</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24.9</v>
+        <v>24.92</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7635</v>
+        <v>0.7654</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>20.71</v>
+        <v>20.73</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5345</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="100">
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25.9</v>
+        <v>25.91</v>
       </c>
       <c r="C100" t="n">
         <v>0.8018999999999999</v>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>26.33</v>
+        <v>26.38</v>
       </c>
       <c r="C101" t="n">
-        <v>0.75</v>
+        <v>0.7521</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>26.04</v>
+        <v>26.08</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7851</v>
+        <v>0.7863</v>
       </c>
     </row>
   </sheetData>
